--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/71.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/71.xlsx
@@ -426,13 +426,13 @@
         <v>-8.241684462331454</v>
       </c>
       <c r="E2">
-        <v>-6.926370998549529</v>
+        <v>-7.517246287070357</v>
       </c>
       <c r="F2">
-        <v>-4.457475791305551</v>
+        <v>-4.553254115519438</v>
       </c>
       <c r="G2">
-        <v>-8.96981173077528</v>
+        <v>-9.132995141497036</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.348504751311966</v>
       </c>
       <c r="E3">
-        <v>-7.523214815812467</v>
+        <v>-7.752432584658717</v>
       </c>
       <c r="F3">
-        <v>-4.66391157502241</v>
+        <v>-4.715252958280521</v>
       </c>
       <c r="G3">
-        <v>-8.716886051574962</v>
+        <v>-9.116985343269119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.441505807211405</v>
       </c>
       <c r="E4">
-        <v>-7.708565256946414</v>
+        <v>-9.043586565251681</v>
       </c>
       <c r="F4">
-        <v>-4.458393622387853</v>
+        <v>-4.214296943070117</v>
       </c>
       <c r="G4">
-        <v>-9.264768096142186</v>
+        <v>-9.484935927231415</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.455589205143273</v>
       </c>
       <c r="E5">
-        <v>-8.233999567582398</v>
+        <v>-8.990938526438507</v>
       </c>
       <c r="F5">
-        <v>-4.410484993646944</v>
+        <v>-4.577487175520935</v>
       </c>
       <c r="G5">
-        <v>-8.781650253959723</v>
+        <v>-9.911671868334551</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.350779274487479</v>
       </c>
       <c r="E6">
-        <v>-8.341247417506056</v>
+        <v>-10.66375229639793</v>
       </c>
       <c r="F6">
-        <v>-4.275745237009784</v>
+        <v>-4.592038277318511</v>
       </c>
       <c r="G6">
-        <v>-9.319431824086632</v>
+        <v>-9.555020176297788</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.091702594676672</v>
       </c>
       <c r="E7">
-        <v>-10.20639000704525</v>
+        <v>-10.85380782202585</v>
       </c>
       <c r="F7">
-        <v>-3.98179326555456</v>
+        <v>-4.284564864747391</v>
       </c>
       <c r="G7">
-        <v>-9.410528105690757</v>
+        <v>-10.28893832744436</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.664263590093463</v>
       </c>
       <c r="E8">
-        <v>-9.273900224807788</v>
+        <v>-10.50735238959502</v>
       </c>
       <c r="F8">
-        <v>-4.061934498305801</v>
+        <v>-4.173582685222521</v>
       </c>
       <c r="G8">
-        <v>-9.448132592471339</v>
+        <v>-10.02956701607908</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.067794820131943</v>
       </c>
       <c r="E9">
-        <v>-11.27387359945136</v>
+        <v>-11.57576884764671</v>
       </c>
       <c r="F9">
-        <v>-4.169884024769021</v>
+        <v>-4.116900817318562</v>
       </c>
       <c r="G9">
-        <v>-9.099167987176763</v>
+        <v>-10.57534355368332</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.324189626866189</v>
       </c>
       <c r="E10">
-        <v>-11.46360760342473</v>
+        <v>-11.33207807587194</v>
       </c>
       <c r="F10">
-        <v>-3.853286145256064</v>
+        <v>-3.80448536482234</v>
       </c>
       <c r="G10">
-        <v>-10.07446794522821</v>
+        <v>-10.92372550296299</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.479919911640381</v>
       </c>
       <c r="E11">
-        <v>-11.57216871081061</v>
+        <v>-12.23667245822215</v>
       </c>
       <c r="F11">
-        <v>-3.773426557421775</v>
+        <v>-3.835330453432982</v>
       </c>
       <c r="G11">
-        <v>-9.512324070477806</v>
+        <v>-10.68765050055756</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.596409128230566</v>
       </c>
       <c r="E12">
-        <v>-12.27406406810348</v>
+        <v>-13.13685610688889</v>
       </c>
       <c r="F12">
-        <v>-3.434562162121567</v>
+        <v>-3.557616968174837</v>
       </c>
       <c r="G12">
-        <v>-9.588499723336437</v>
+        <v>-10.27455400707622</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.742449998917441</v>
       </c>
       <c r="E13">
-        <v>-12.6381035651061</v>
+        <v>-13.7861124823166</v>
       </c>
       <c r="F13">
-        <v>-3.142054035049423</v>
+        <v>-3.605919071432076</v>
       </c>
       <c r="G13">
-        <v>-9.542486450886106</v>
+        <v>-9.973433405915193</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.99737995650025</v>
       </c>
       <c r="E14">
-        <v>-13.25974077756103</v>
+        <v>-15.0854947001815</v>
       </c>
       <c r="F14">
-        <v>-3.119843848245563</v>
+        <v>-3.054064849524059</v>
       </c>
       <c r="G14">
-        <v>-9.349455161582283</v>
+        <v>-10.03207972014338</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.429103049210417</v>
       </c>
       <c r="E15">
-        <v>-13.26975323359199</v>
+        <v>-15.45010025643507</v>
       </c>
       <c r="F15">
-        <v>-2.776386155696831</v>
+        <v>-2.773409831618573</v>
       </c>
       <c r="G15">
-        <v>-9.268012430770671</v>
+        <v>-9.961479025972885</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.084711626572491</v>
       </c>
       <c r="E16">
-        <v>-14.42735345875074</v>
+        <v>-15.60581636366283</v>
       </c>
       <c r="F16">
-        <v>-2.5922988961401</v>
+        <v>-2.593290451921251</v>
       </c>
       <c r="G16">
-        <v>-9.302968481119835</v>
+        <v>-9.002764901073185</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.994810706610163</v>
       </c>
       <c r="E17">
-        <v>-15.40983759403288</v>
+        <v>-17.22874446395375</v>
       </c>
       <c r="F17">
-        <v>-2.244223055320762</v>
+        <v>-2.675037889066521</v>
       </c>
       <c r="G17">
-        <v>-7.795736686909371</v>
+        <v>-8.350289480738228</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.160882319781478</v>
       </c>
       <c r="E18">
-        <v>-15.83773310301765</v>
+        <v>-17.56884191887781</v>
       </c>
       <c r="F18">
-        <v>-1.885206137845248</v>
+        <v>-1.834119891747199</v>
       </c>
       <c r="G18">
-        <v>-7.660001009253714</v>
+        <v>-8.71697874685006</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.554589049450563</v>
       </c>
       <c r="E19">
-        <v>-16.53586529841015</v>
+        <v>-18.37026860638527</v>
       </c>
       <c r="F19">
-        <v>-1.629285342219952</v>
+        <v>-1.822140870735316</v>
       </c>
       <c r="G19">
-        <v>-7.100061957832463</v>
+        <v>-8.074630285319733</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.133694320785425</v>
       </c>
       <c r="E20">
-        <v>-17.69453424343471</v>
+        <v>-18.77108836927819</v>
       </c>
       <c r="F20">
-        <v>-1.704831620987864</v>
+        <v>-1.766000755112788</v>
       </c>
       <c r="G20">
-        <v>-6.748736933568387</v>
+        <v>-7.698770808064118</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.840625088349751</v>
       </c>
       <c r="E21">
-        <v>-18.46351441467721</v>
+        <v>-19.91480882160343</v>
       </c>
       <c r="F21">
-        <v>-1.643429715622753</v>
+        <v>-1.185913287015156</v>
       </c>
       <c r="G21">
-        <v>-6.72392108420601</v>
+        <v>-6.988297940426668</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.606371153999439</v>
       </c>
       <c r="E22">
-        <v>-19.35297463689379</v>
+        <v>-21.11635335853261</v>
       </c>
       <c r="F22">
-        <v>-0.9813139938303029</v>
+        <v>-1.354843908202864</v>
       </c>
       <c r="G22">
-        <v>-6.170368075130014</v>
+        <v>-7.406651580224368</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.36480774451104</v>
       </c>
       <c r="E23">
-        <v>-19.77934857861198</v>
+        <v>-21.10581559951676</v>
       </c>
       <c r="F23">
-        <v>-1.01754595566135</v>
+        <v>-1.034732094167232</v>
       </c>
       <c r="G23">
-        <v>-5.384500843381202</v>
+        <v>-6.452045842338904</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.057749717802441</v>
       </c>
       <c r="E24">
-        <v>-20.15275748833647</v>
+        <v>-22.73722100315004</v>
       </c>
       <c r="F24">
-        <v>-0.8943992008263704</v>
+        <v>-0.739869746936331</v>
       </c>
       <c r="G24">
-        <v>-5.683267646663809</v>
+        <v>-6.913304152325558</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.634511288681353</v>
       </c>
       <c r="E25">
-        <v>-21.40084115264248</v>
+        <v>-23.06370586520705</v>
       </c>
       <c r="F25">
-        <v>-0.4956446706711611</v>
+        <v>-0.6276234787547895</v>
       </c>
       <c r="G25">
-        <v>-5.734134178874711</v>
+        <v>-6.74986251905174</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.057972701778916</v>
       </c>
       <c r="E26">
-        <v>-21.82480594618859</v>
+        <v>-23.54000623285981</v>
       </c>
       <c r="F26">
-        <v>-0.7054568799218311</v>
+        <v>-0.5605066666777653</v>
       </c>
       <c r="G26">
-        <v>-5.213991195381039</v>
+        <v>-6.718558000432391</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.306699381955716</v>
       </c>
       <c r="E27">
-        <v>-21.93598904002491</v>
+        <v>-23.88223207056747</v>
       </c>
       <c r="F27">
-        <v>-1.063638803055323</v>
+        <v>-0.7186743102009</v>
       </c>
       <c r="G27">
-        <v>-5.807578631663442</v>
+        <v>-6.497115609310542</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.370304473211977</v>
       </c>
       <c r="E28">
-        <v>-22.00570942584701</v>
+        <v>-24.17119399699692</v>
       </c>
       <c r="F28">
-        <v>-1.058272639019988</v>
+        <v>-0.7915557310340061</v>
       </c>
       <c r="G28">
-        <v>-4.986424295011538</v>
+        <v>-7.114711121843738</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.250850301300806</v>
       </c>
       <c r="E29">
-        <v>-22.64636170066015</v>
+        <v>-23.73324074724111</v>
       </c>
       <c r="F29">
-        <v>-1.186226409893414</v>
+        <v>-0.4941039073019541</v>
       </c>
       <c r="G29">
-        <v>-5.707520703284509</v>
+        <v>-7.285300222936844</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.963363138705501</v>
       </c>
       <c r="E30">
-        <v>-21.80380741221502</v>
+        <v>-23.37737967429635</v>
       </c>
       <c r="F30">
-        <v>-1.092188485592808</v>
+        <v>-0.8306836653052407</v>
       </c>
       <c r="G30">
-        <v>-5.967812346309707</v>
+        <v>-6.810011820954758</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.531616809514019</v>
       </c>
       <c r="E31">
-        <v>-21.76410628058978</v>
+        <v>-24.33609384951222</v>
       </c>
       <c r="F31">
-        <v>-1.329931586931072</v>
+        <v>-1.164862814575214</v>
       </c>
       <c r="G31">
-        <v>-5.649324623249662</v>
+        <v>-7.133081339041154</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.984948750463865</v>
       </c>
       <c r="E32">
-        <v>-21.41459412820377</v>
+        <v>-23.47381352828969</v>
       </c>
       <c r="F32">
-        <v>-1.373720744577859</v>
+        <v>-1.36258334484722</v>
       </c>
       <c r="G32">
-        <v>-5.785116580179487</v>
+        <v>-6.684959273754328</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.355882982517127</v>
       </c>
       <c r="E33">
-        <v>-21.99769855532744</v>
+        <v>-23.55934734534657</v>
       </c>
       <c r="F33">
-        <v>-1.576864596235994</v>
+        <v>-1.381371545910116</v>
       </c>
       <c r="G33">
-        <v>-5.926768202713823</v>
+        <v>-6.672541417436522</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.679812917167003</v>
       </c>
       <c r="E34">
-        <v>-21.30300800018077</v>
+        <v>-23.1010476618743</v>
       </c>
       <c r="F34">
-        <v>-1.634290338067666</v>
+        <v>-1.214759525082843</v>
       </c>
       <c r="G34">
-        <v>-5.632742100643452</v>
+        <v>-6.322517437569379</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.991187046511429</v>
       </c>
       <c r="E35">
-        <v>-20.54445237610392</v>
+        <v>-22.06352898197694</v>
       </c>
       <c r="F35">
-        <v>-1.416882828100728</v>
+        <v>-1.456271698103844</v>
       </c>
       <c r="G35">
-        <v>-5.638873230982182</v>
+        <v>-6.180988305219996</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.320598435402252</v>
       </c>
       <c r="E36">
-        <v>-20.8582303400954</v>
+        <v>-22.62839271579771</v>
       </c>
       <c r="F36">
-        <v>-1.588120452505233</v>
+        <v>-1.558153433341558</v>
       </c>
       <c r="G36">
-        <v>-5.383292494259369</v>
+        <v>-6.08744221991681</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.699264251848823</v>
       </c>
       <c r="E37">
-        <v>-20.8653174019174</v>
+        <v>-22.57356648098684</v>
       </c>
       <c r="F37">
-        <v>-1.774847718974687</v>
+        <v>-1.977181427312882</v>
       </c>
       <c r="G37">
-        <v>-4.546697773212304</v>
+        <v>-5.724212473893515</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.152045074884865</v>
       </c>
       <c r="E38">
-        <v>-19.96542810406116</v>
+        <v>-21.83574673939112</v>
       </c>
       <c r="F38">
-        <v>-1.840888481795474</v>
+        <v>-1.931578145053964</v>
       </c>
       <c r="G38">
-        <v>-4.659494680826351</v>
+        <v>-5.590820662479661</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.69303741245037</v>
       </c>
       <c r="E39">
-        <v>-20.13306768335111</v>
+        <v>-22.61641943052143</v>
       </c>
       <c r="F39">
-        <v>-2.139039447615489</v>
+        <v>-1.957323803932973</v>
       </c>
       <c r="G39">
-        <v>-4.37632716812479</v>
+        <v>-4.873395649209741</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.333104646061217</v>
       </c>
       <c r="E40">
-        <v>-20.5629194931072</v>
+        <v>-21.80824984521655</v>
       </c>
       <c r="F40">
-        <v>-2.369174822726442</v>
+        <v>-2.445817031568258</v>
       </c>
       <c r="G40">
-        <v>-4.168206412252968</v>
+        <v>-5.248493700991324</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.072413232397846</v>
       </c>
       <c r="E41">
-        <v>-19.87404349858638</v>
+        <v>-21.41672251098738</v>
       </c>
       <c r="F41">
-        <v>-2.090289197593335</v>
+        <v>-1.982378604398047</v>
       </c>
       <c r="G41">
-        <v>-3.620767980788006</v>
+        <v>-4.478523708922092</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.9009034744961072</v>
       </c>
       <c r="E42">
-        <v>-19.71484952332073</v>
+        <v>-21.49861543494209</v>
       </c>
       <c r="F42">
-        <v>-2.21810048927348</v>
+        <v>-2.264596751592616</v>
       </c>
       <c r="G42">
-        <v>-3.798772703889079</v>
+        <v>-5.212729877530577</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8059392905432897</v>
       </c>
       <c r="E43">
-        <v>-19.37658610036978</v>
+        <v>-20.77361127478807</v>
       </c>
       <c r="F43">
-        <v>-2.232696322910807</v>
+        <v>-2.278380785175199</v>
       </c>
       <c r="G43">
-        <v>-4.370172863967285</v>
+        <v>-4.583044252687962</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7706815110561649</v>
       </c>
       <c r="E44">
-        <v>-18.7508460904639</v>
+        <v>-20.81570796916337</v>
       </c>
       <c r="F44">
-        <v>-2.536905139547494</v>
+        <v>-2.581354506014313</v>
       </c>
       <c r="G44">
-        <v>-3.462801989836142</v>
+        <v>-4.446060499363999</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7733166431409193</v>
       </c>
       <c r="E45">
-        <v>-17.90455128248844</v>
+        <v>-20.304805531618</v>
       </c>
       <c r="F45">
-        <v>-2.342702685635178</v>
+        <v>-2.332267741462113</v>
       </c>
       <c r="G45">
-        <v>-3.234808029092075</v>
+        <v>-4.384149987234088</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7909913155889641</v>
       </c>
       <c r="E46">
-        <v>-17.91705439922362</v>
+        <v>-20.49685811428331</v>
       </c>
       <c r="F46">
-        <v>-2.791183282613039</v>
+        <v>-2.669159793976255</v>
       </c>
       <c r="G46">
-        <v>-3.681380759066522</v>
+        <v>-4.060127032032382</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.803921616004262</v>
       </c>
       <c r="E47">
-        <v>-18.2267612650822</v>
+        <v>-19.66826058272982</v>
       </c>
       <c r="F47">
-        <v>-2.473774431412741</v>
+        <v>-2.747143958010606</v>
       </c>
       <c r="G47">
-        <v>-2.862758989752161</v>
+        <v>-3.870346698448122</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7959521807157893</v>
       </c>
       <c r="E48">
-        <v>-18.23116747029166</v>
+        <v>-19.90632246131305</v>
       </c>
       <c r="F48">
-        <v>-2.704603150039838</v>
+        <v>-2.482427557302385</v>
       </c>
       <c r="G48">
-        <v>-2.911675610640432</v>
+        <v>-3.732594898559047</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7572494517197831</v>
       </c>
       <c r="E49">
-        <v>-18.04682687886143</v>
+        <v>-18.64258386236252</v>
       </c>
       <c r="F49">
-        <v>-2.840381679400108</v>
+        <v>-3.063121390338866</v>
       </c>
       <c r="G49">
-        <v>-3.145009481339344</v>
+        <v>-3.923702760904555</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.6859935325970011</v>
       </c>
       <c r="E50">
-        <v>-17.54066575360209</v>
+        <v>-18.53592471405986</v>
       </c>
       <c r="F50">
-        <v>-2.877524845374234</v>
+        <v>-2.851997047122162</v>
       </c>
       <c r="G50">
-        <v>-2.950948612372806</v>
+        <v>-3.399871829680136</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5852082123950533</v>
       </c>
       <c r="E51">
-        <v>-17.01935688278709</v>
+        <v>-18.63768858196023</v>
       </c>
       <c r="F51">
-        <v>-2.747185376380746</v>
+        <v>-2.914535472563914</v>
       </c>
       <c r="G51">
-        <v>-2.539401454203848</v>
+        <v>-4.166650455849511</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.4639973536415721</v>
       </c>
       <c r="E52">
-        <v>-17.67407459786806</v>
+        <v>-18.43331402152006</v>
       </c>
       <c r="F52">
-        <v>-3.161559602283143</v>
+        <v>-3.084377297894702</v>
       </c>
       <c r="G52">
-        <v>-3.121504608010518</v>
+        <v>-4.166855709672945</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.3379997465629792</v>
       </c>
       <c r="E53">
-        <v>-15.96389638887135</v>
+        <v>-17.84114358943304</v>
       </c>
       <c r="F53">
-        <v>-3.19660202852377</v>
+        <v>-2.959542330292816</v>
       </c>
       <c r="G53">
-        <v>-2.538193105082014</v>
+        <v>-3.212319493243806</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.2252094978595137</v>
       </c>
       <c r="E54">
-        <v>-15.60751906988971</v>
+        <v>-18.12666387561665</v>
       </c>
       <c r="F54">
-        <v>-3.280144537830906</v>
+        <v>-3.178092158908215</v>
       </c>
       <c r="G54">
-        <v>-3.003457175171186</v>
+        <v>-4.104590969170333</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.14343127362297</v>
       </c>
       <c r="E55">
-        <v>-15.84428580490675</v>
+        <v>-17.34611798175856</v>
       </c>
       <c r="F55">
-        <v>-3.302941208755949</v>
+        <v>-3.317240486863073</v>
       </c>
       <c r="G55">
-        <v>-2.605609054443732</v>
+        <v>-4.224088420955866</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.1091944866548483</v>
       </c>
       <c r="E56">
-        <v>-15.12698457903978</v>
+        <v>-17.82186587558239</v>
       </c>
       <c r="F56">
-        <v>-3.075957771612647</v>
+        <v>-3.167162679395679</v>
       </c>
       <c r="G56">
-        <v>-3.206675013099348</v>
+        <v>-3.652449901598831</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.1340739899187279</v>
       </c>
       <c r="E57">
-        <v>-16.00469341120645</v>
+        <v>-16.38014013423438</v>
       </c>
       <c r="F57">
-        <v>-3.361645949857544</v>
+        <v>-3.471400488891464</v>
       </c>
       <c r="G57">
-        <v>-3.122822205135148</v>
+        <v>-3.673011699943245</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.2238693934513187</v>
       </c>
       <c r="E58">
-        <v>-15.90393033606177</v>
+        <v>-15.88541340584441</v>
       </c>
       <c r="F58">
-        <v>-3.36066847632224</v>
+        <v>-3.179113535915867</v>
       </c>
       <c r="G58">
-        <v>-3.239230917932541</v>
+        <v>-4.65609806110306</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.3812541871132615</v>
       </c>
       <c r="E59">
-        <v>-14.55718933702466</v>
+        <v>-16.17457005665619</v>
       </c>
       <c r="F59">
-        <v>-3.25296166150804</v>
+        <v>-3.598646005635497</v>
       </c>
       <c r="G59">
-        <v>-3.438459548485881</v>
+        <v>-5.009250506504813</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.6021401052100886</v>
       </c>
       <c r="E60">
-        <v>-15.06118585170833</v>
+        <v>-16.31728491500792</v>
       </c>
       <c r="F60">
-        <v>-3.544412791774213</v>
+        <v>-3.520372741377568</v>
       </c>
       <c r="G60">
-        <v>-3.360764355224726</v>
+        <v>-4.782908507984843</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.874591321121663</v>
       </c>
       <c r="E61">
-        <v>-14.87814493231829</v>
+        <v>-15.70796968032785</v>
       </c>
       <c r="F61">
-        <v>-3.461943018253702</v>
+        <v>-3.630395671449996</v>
       </c>
       <c r="G61">
-        <v>-3.462990690931881</v>
+        <v>-4.612772951630618</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.182108682168863</v>
       </c>
       <c r="E62">
-        <v>-14.48871881002868</v>
+        <v>-15.76728816135433</v>
       </c>
       <c r="F62">
-        <v>-3.378325127512912</v>
+        <v>-3.380621361953472</v>
       </c>
       <c r="G62">
-        <v>-4.257524930902505</v>
+        <v>-5.455349828467145</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.505148199684889</v>
       </c>
       <c r="E63">
-        <v>-14.09792056011474</v>
+        <v>-15.42259430531248</v>
       </c>
       <c r="F63">
-        <v>-3.219397042714007</v>
+        <v>-3.630005510403277</v>
       </c>
       <c r="G63">
-        <v>-4.5580694971397</v>
+        <v>-5.090219829304308</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.822423698142993</v>
       </c>
       <c r="E64">
-        <v>-14.66776108686994</v>
+        <v>-14.72897247003162</v>
       </c>
       <c r="F64">
-        <v>-3.346800777631974</v>
+        <v>-3.491972164972587</v>
       </c>
       <c r="G64">
-        <v>-4.717094862664131</v>
+        <v>-5.958546129345287</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.114695762874565</v>
       </c>
       <c r="E65">
-        <v>-13.99510155777059</v>
+        <v>-14.60859657395973</v>
       </c>
       <c r="F65">
-        <v>-3.491229947779679</v>
+        <v>-3.682216679434327</v>
       </c>
       <c r="G65">
-        <v>-4.975847102013567</v>
+        <v>-5.642508209984302</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.366531256957616</v>
       </c>
       <c r="E66">
-        <v>-13.84899940086112</v>
+        <v>-15.2352151078231</v>
       </c>
       <c r="F66">
-        <v>-3.506788344339059</v>
+        <v>-3.649934373379828</v>
       </c>
       <c r="G66">
-        <v>-4.859646953585148</v>
+        <v>-6.38406378968997</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.565982961304171</v>
       </c>
       <c r="E67">
-        <v>-13.85398072226956</v>
+        <v>-15.17680232159816</v>
       </c>
       <c r="F67">
-        <v>-3.43020743468505</v>
+        <v>-3.757921176376174</v>
       </c>
       <c r="G67">
-        <v>-5.465533066545943</v>
+        <v>-6.275646733824377</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.705838511725033</v>
       </c>
       <c r="E68">
-        <v>-12.9003520233643</v>
+        <v>-14.35509259901034</v>
       </c>
       <c r="F68">
-        <v>-3.448464652242752</v>
+        <v>-3.542661623084695</v>
       </c>
       <c r="G68">
-        <v>-5.452757671309896</v>
+        <v>-6.705964685201003</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.785030951458023</v>
       </c>
       <c r="E69">
-        <v>-13.75549546955074</v>
+        <v>-15.34298826073165</v>
       </c>
       <c r="F69">
-        <v>-3.42423324897606</v>
+        <v>-3.744074186870978</v>
       </c>
       <c r="G69">
-        <v>-5.208793638884384</v>
+        <v>-6.995140838056342</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.805980375476278</v>
       </c>
       <c r="E70">
-        <v>-13.68627321586949</v>
+        <v>-14.42867577316098</v>
       </c>
       <c r="F70">
-        <v>-3.611732553864923</v>
+        <v>-3.767712479077264</v>
       </c>
       <c r="G70">
-        <v>-5.755311738689429</v>
+        <v>-6.976154859388622</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.774754252880288</v>
       </c>
       <c r="E71">
-        <v>-14.27276041307689</v>
+        <v>-14.81650334412588</v>
       </c>
       <c r="F71">
-        <v>-3.441636419741475</v>
+        <v>-3.689802868109165</v>
       </c>
       <c r="G71">
-        <v>-5.358403812895127</v>
+        <v>-6.210081379419112</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.701833751646693</v>
       </c>
       <c r="E72">
-        <v>-14.13065689871619</v>
+        <v>-14.86812794781333</v>
       </c>
       <c r="F72">
-        <v>-3.612917119250926</v>
+        <v>-3.86790517318067</v>
       </c>
       <c r="G72">
-        <v>-5.550359174898689</v>
+        <v>-6.887683840397139</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.599369625225953</v>
       </c>
       <c r="E73">
-        <v>-13.80719705729631</v>
+        <v>-14.77897135155031</v>
       </c>
       <c r="F73">
-        <v>-3.611110449945421</v>
+        <v>-3.977902423863611</v>
       </c>
       <c r="G73">
-        <v>-5.048755246424936</v>
+        <v>-6.430997393800217</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.480289935283014</v>
       </c>
       <c r="E74">
-        <v>-15.20526378073637</v>
+        <v>-15.46638917744066</v>
       </c>
       <c r="F74">
-        <v>-3.685747181305059</v>
+        <v>-3.935622551624724</v>
       </c>
       <c r="G74">
-        <v>-5.874501309739809</v>
+        <v>-6.616474018183425</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.358292887072774</v>
       </c>
       <c r="E75">
-        <v>-15.2060517352137</v>
+        <v>-15.41111462370304</v>
       </c>
       <c r="F75">
-        <v>-3.78800085350663</v>
+        <v>-4.086630615685463</v>
       </c>
       <c r="G75">
-        <v>-5.362965744648243</v>
+        <v>-7.279387588603705</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.248833006309267</v>
       </c>
       <c r="E76">
-        <v>-15.39265203517377</v>
+        <v>-16.36707095824825</v>
       </c>
       <c r="F76">
-        <v>-3.919378266855826</v>
+        <v>-4.281678004348635</v>
       </c>
       <c r="G76">
-        <v>-4.799411577498109</v>
+        <v>-6.533018475683938</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.163934105101879</v>
       </c>
       <c r="E77">
-        <v>-14.79918645952055</v>
+        <v>-16.45844650677502</v>
       </c>
       <c r="F77">
-        <v>-3.859334884031306</v>
+        <v>-4.100626711323163</v>
       </c>
       <c r="G77">
-        <v>-4.94848544313149</v>
+        <v>-6.684436207559123</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.109868954260631</v>
       </c>
       <c r="E78">
-        <v>-15.94176573639586</v>
+        <v>-16.12001553028578</v>
       </c>
       <c r="F78">
-        <v>-3.912559974763383</v>
+        <v>-4.334595770774272</v>
       </c>
       <c r="G78">
-        <v>-5.036814108664785</v>
+        <v>-6.270608083513607</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.090770631361488</v>
       </c>
       <c r="E79">
-        <v>-16.79128481786478</v>
+        <v>-17.2421125192244</v>
       </c>
       <c r="F79">
-        <v>-4.10215836265094</v>
+        <v>-4.41543117540906</v>
       </c>
       <c r="G79">
-        <v>-4.863705682416295</v>
+        <v>-6.75935385311283</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.105885659570788</v>
       </c>
       <c r="E80">
-        <v>-16.83407436876326</v>
+        <v>-17.7961939564329</v>
       </c>
       <c r="F80">
-        <v>-4.177416369562677</v>
+        <v>-4.41039221649783</v>
       </c>
       <c r="G80">
-        <v>-4.797474908357636</v>
+        <v>-5.740417594308248</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.151192281108906</v>
       </c>
       <c r="E81">
-        <v>-16.64402337160935</v>
+        <v>-17.73920311104637</v>
       </c>
       <c r="F81">
-        <v>-4.133642122529141</v>
+        <v>-4.387236862487375</v>
       </c>
       <c r="G81">
-        <v>-4.588801291380754</v>
+        <v>-5.399259255395274</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.225868419250565</v>
       </c>
       <c r="E82">
-        <v>-19.02610938302014</v>
+        <v>-19.43767974320726</v>
       </c>
       <c r="F82">
-        <v>-4.183248904445788</v>
+        <v>-4.602052410850955</v>
       </c>
       <c r="G82">
-        <v>-4.884115195665902</v>
+        <v>-5.942748206031885</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.327824347319587</v>
       </c>
       <c r="E83">
-        <v>-19.26551168990964</v>
+        <v>-20.47835024101396</v>
       </c>
       <c r="F83">
-        <v>-4.367422314212411</v>
+        <v>-4.374495743464916</v>
       </c>
       <c r="G83">
-        <v>-4.997339163654515</v>
+        <v>-5.844914964255342</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.452517498128884</v>
       </c>
       <c r="E84">
-        <v>-20.14058495020384</v>
+        <v>-21.17854742055395</v>
       </c>
       <c r="F84">
-        <v>-4.215829422765296</v>
+        <v>-4.676925226920391</v>
       </c>
       <c r="G84">
-        <v>-4.375850449567135</v>
+        <v>-5.838466021544843</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.596542137271896</v>
       </c>
       <c r="E85">
-        <v>-20.95573744242856</v>
+        <v>-21.4067598681705</v>
       </c>
       <c r="F85">
-        <v>-4.377187109156612</v>
+        <v>-4.994521289153721</v>
       </c>
       <c r="G85">
-        <v>-5.12000811806667</v>
+        <v>-5.952484520462881</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.755903645732388</v>
       </c>
       <c r="E86">
-        <v>-21.82709735403647</v>
+        <v>-23.07550706847104</v>
       </c>
       <c r="F86">
-        <v>-4.505620504756259</v>
+        <v>-4.66794158243703</v>
       </c>
       <c r="G86">
-        <v>-4.583060805415658</v>
+        <v>-5.38201462368121</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.924071087703976</v>
       </c>
       <c r="E87">
-        <v>-23.77134332754165</v>
+        <v>-24.445180259883</v>
       </c>
       <c r="F87">
-        <v>-4.24603584010838</v>
+        <v>-4.795696545133784</v>
       </c>
       <c r="G87">
-        <v>-4.200388225440223</v>
+        <v>-5.290127121693199</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.095222677067759</v>
       </c>
       <c r="E88">
-        <v>-25.79422172371601</v>
+        <v>-24.25261595965483</v>
       </c>
       <c r="F88">
-        <v>-4.346929333034554</v>
+        <v>-4.796496748044888</v>
       </c>
       <c r="G88">
-        <v>-4.668741034517536</v>
+        <v>-6.08140378485318</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.266425901411931</v>
       </c>
       <c r="E89">
-        <v>-26.68490010544065</v>
+        <v>-27.12570176534728</v>
       </c>
       <c r="F89">
-        <v>-4.480824154920858</v>
+        <v>-4.765418059826656</v>
       </c>
       <c r="G89">
-        <v>-4.555940816357949</v>
+        <v>-5.756427392536163</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.434250636013938</v>
       </c>
       <c r="E90">
-        <v>-28.11116110805246</v>
+        <v>-28.65647089110811</v>
       </c>
       <c r="F90">
-        <v>-4.372978174382988</v>
+        <v>-5.033689813427693</v>
       </c>
       <c r="G90">
-        <v>-4.236575798729997</v>
+        <v>-6.120607265129229</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.597073721140464</v>
       </c>
       <c r="E91">
-        <v>-29.25727259465375</v>
+        <v>-30.55892131375949</v>
       </c>
       <c r="F91">
-        <v>-4.414937468436991</v>
+        <v>-4.991606264263269</v>
       </c>
       <c r="G91">
-        <v>-5.098413429514004</v>
+        <v>-6.069618242733374</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.758956863033784</v>
       </c>
       <c r="E92">
-        <v>-31.37388587431288</v>
+        <v>-32.29021353281696</v>
       </c>
       <c r="F92">
-        <v>-4.161667448500653</v>
+        <v>-4.752430915685565</v>
       </c>
       <c r="G92">
-        <v>-4.606029370367122</v>
+        <v>-6.237429796119031</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.923612842103714</v>
       </c>
       <c r="E93">
-        <v>-33.77657870669558</v>
+        <v>-34.12743128738786</v>
       </c>
       <c r="F93">
-        <v>-4.232706580229933</v>
+        <v>-4.274669187753548</v>
       </c>
       <c r="G93">
-        <v>-5.972324619879734</v>
+        <v>-7.279039981322081</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.092784270751894</v>
       </c>
       <c r="E94">
-        <v>-35.64531011188585</v>
+        <v>-35.60337191410081</v>
       </c>
       <c r="F94">
-        <v>-4.191123364976801</v>
+        <v>-4.675661966631122</v>
       </c>
       <c r="G94">
-        <v>-5.702346320606629</v>
+        <v>-7.367765912320088</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.271948356114085</v>
       </c>
       <c r="E95">
-        <v>-37.85010636589634</v>
+        <v>-38.24586103061168</v>
       </c>
       <c r="F95">
-        <v>-3.858884252164184</v>
+        <v>-4.375346476787591</v>
       </c>
       <c r="G95">
-        <v>-5.883542409607559</v>
+        <v>-7.501634442291597</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.462396682173701</v>
       </c>
       <c r="E96">
-        <v>-40.30530459016097</v>
+        <v>-40.44540878324728</v>
       </c>
       <c r="F96">
-        <v>-3.926032542202514</v>
+        <v>-4.121060878415421</v>
       </c>
       <c r="G96">
-        <v>-6.687442182908781</v>
+        <v>-7.792624774102457</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.659558360820319</v>
       </c>
       <c r="E97">
-        <v>-41.86131543004056</v>
+        <v>-42.50843889421066</v>
       </c>
       <c r="F97">
-        <v>-3.64633097517765</v>
+        <v>-3.813854200148002</v>
       </c>
       <c r="G97">
-        <v>-7.077394652525074</v>
+        <v>-7.732690657659491</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.858441796156012</v>
       </c>
       <c r="E98">
-        <v>-44.41441473387701</v>
+        <v>-44.64440913601558</v>
       </c>
       <c r="F98">
-        <v>-3.611497297522528</v>
+        <v>-3.801347509100535</v>
       </c>
       <c r="G98">
-        <v>-6.746141465865598</v>
+        <v>-8.212163589203215</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.048931439201064</v>
       </c>
       <c r="E99">
-        <v>-47.04730574972861</v>
+        <v>-47.1882771455874</v>
       </c>
       <c r="F99">
-        <v>-3.516360129678408</v>
+        <v>-3.904118910928856</v>
       </c>
       <c r="G99">
-        <v>-7.690107110387846</v>
+        <v>-8.90126688538467</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.217730155043058</v>
       </c>
       <c r="E100">
-        <v>-49.25080006746191</v>
+        <v>-49.5563158306264</v>
       </c>
       <c r="F100">
-        <v>-3.3257701860097</v>
+        <v>-3.790770914101592</v>
       </c>
       <c r="G100">
-        <v>-7.806525754821856</v>
+        <v>-9.350802553616765</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.345599697426779</v>
       </c>
       <c r="E101">
-        <v>-51.27234822439652</v>
+        <v>-51.95831354224892</v>
       </c>
       <c r="F101">
-        <v>-3.381926040612881</v>
+        <v>-3.461050866560887</v>
       </c>
       <c r="G101">
-        <v>-8.361581751572681</v>
+        <v>-9.674136915346304</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.42118287085187</v>
       </c>
       <c r="E102">
-        <v>-53.76686379211424</v>
+        <v>-53.19408654996507</v>
       </c>
       <c r="F102">
-        <v>-2.924137907497165</v>
+        <v>-3.637802932765829</v>
       </c>
       <c r="G102">
-        <v>-9.156357661367672</v>
+        <v>-10.45773973394626</v>
       </c>
     </row>
   </sheetData>
